--- a/output/pdf_financials_xlsx/GGO.xlsx
+++ b/output/pdf_financials_xlsx/GGO.xlsx
@@ -6076,25 +6076,25 @@
         <v>11.720793</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>12.035229</v>
+        <v>12.035391</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>12.242866</v>
+        <v>12.257405</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>12.282236</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>12.325856</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.136202</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.044123</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.014775</v>
       </c>
       <c r="K92" s="3" t="n">
         <v>0</v>
@@ -6106,19 +6106,19 @@
         <v>0</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>8.520673</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>7.531016</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>3.047191</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>2.830638</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>2.245865</v>
       </c>
     </row>
     <row r="93">
@@ -11557,7 +11557,11 @@
           <t>Reserves 15</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>-</t>
@@ -13303,7 +13307,11 @@
           <t>Reserves 13</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>-</t>
@@ -19317,7 +19325,11 @@
           <t>Reserves 11</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr"/>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
           <t>-</t>
@@ -21111,7 +21123,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr"/>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E124" t="inlineStr">
         <is>
           <t>-</t>
@@ -22283,7 +22299,11 @@
           <t>Reserves 4</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr"/>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E136" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/GGO.xlsx
+++ b/output/pdf_financials_xlsx/GGO.xlsx
@@ -1120,31 +1120,31 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.031038</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.028315</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.011831</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.00928</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.003828</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.002613</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.000183</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.000228</v>
       </c>
       <c r="N12" s="3" t="n">
         <v>0</v>
@@ -2166,31 +2166,31 @@
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-1.355694</v>
+        <v>-1.386732</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-1.32588</v>
+        <v>-1.354195</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-16.183263</v>
+        <v>-16.195094</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-1.254283</v>
+        <v>-1.263563</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-28.703068</v>
+        <v>-28.706896</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-2.502504</v>
+        <v>-2.505117</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>0.107219</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.734621</v>
+        <v>-0.734804</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-1.324338</v>
+        <v>-1.324566</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>-0.34466</v>
@@ -2298,31 +2298,31 @@
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.351544</v>
+        <v>-1.382582</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-1.320198</v>
+        <v>-1.348513</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-16.178934</v>
+        <v>-16.190765</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-1.251113</v>
+        <v>-1.260393</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-28.70073</v>
+        <v>-28.704558</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-2.500142</v>
+        <v>-2.502755</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>0.108516</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.7337129999999999</v>
+        <v>-0.733896</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-1.323703</v>
+        <v>-1.323931</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>-0.30759</v>
@@ -2633,19 +2633,19 @@
         <v>0.247666</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.565754</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.26934</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>1.58129</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>1.074656</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.517218</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>0.26049</v>
@@ -2749,19 +2749,19 @@
         <v>0.247666</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.565754</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.26934</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>1.58129</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0.544084</v>
+        <v>1.61874</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0.753112</v>
+        <v>1.27033</v>
       </c>
       <c r="P36" s="3" t="n">
         <v>0.672741</v>
@@ -3445,19 +3445,19 @@
         <v>0.095388</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.571313</v>
+        <v>0.005559</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.274869</v>
+        <v>0.005529</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>2.103416</v>
+        <v>0.522126</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>1.307954</v>
+        <v>0.233298</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.817788</v>
+        <v>0.30057</v>
       </c>
       <c r="P48" s="3" t="n">
         <v>0.103846</v>
@@ -13600,7 +13600,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -14196,7 +14196,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -57359,7 +57359,7 @@
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E488" t="inlineStr">
@@ -60979,7 +60979,7 @@
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E524" t="inlineStr">
@@ -66092,7 +66092,7 @@
       </c>
       <c r="D575" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E575" t="inlineStr">
@@ -71213,7 +71213,7 @@
       </c>
       <c r="D626" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E626" t="inlineStr">
@@ -74550,7 +74550,7 @@
       </c>
       <c r="D659" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E659" t="inlineStr">
